--- a/papers/P001-sut-to-sam/outputs/P001_SA_SAM_2019_v02.xlsx
+++ b/papers/P001-sut-to-sam/outputs/P001_SA_SAM_2019_v02.xlsx
@@ -447,7 +447,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated by papers/P001-za-sam/code/12_generate_workbook.py.</t>
+          <t>Generated by papers/P001-sut-to-sam/code/12_generate_workbook.py.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S-003 — UNU-WIDER 2019 South Africa SAM (benchmark) — PENDING</t>
+          <t>S-003 — UNU-WIDER 2019 South Africa SAM (benchmark) — OBTAINED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -656,7 +656,11 @@
           <t>A 2019 Social Accounting Matrix for South Africa with occupational and capital stock detail</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>515f98108a8951d02f9808903e319e7fee5e44f67b9b71839392e9c7966b2d99; 8a79715cc9d39194fc55afa8e7968f1f36d071a88bc4a067e033d5f7e17cc144</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,7 +682,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S-005 — Stats SA Labour Market Dynamics 2018 &amp; 2019 — PENDING</t>
+          <t>S-005 — Stats SA Labour Market Dynamics 2018 &amp; 2019 — OBTAINED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -691,7 +695,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S-006 — Stats SA Living Conditions Survey 2014/15 (P0310) — PENDING</t>
+          <t>S-006 — Stats SA Living Conditions Survey 2014/15 (P0310) — OBTAINED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -704,7 +708,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S-007 — Stats SA Annual Financial Statistics 2019 (P0021) — PENDING</t>
+          <t>S-007 — Stats SA Annual Financial Statistics 2019 (P0021) — OBTAINED</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -773,7 +777,11 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cefd02794843d898f85b2e87c492d7798f62b7fea91a9f84f9ffbb2c7340ba1f; f0bdbb317792fd7da61a6141bc523e52287063acd4a061ed6a3b1c429b58810a; aaa52b563491bb3606e58a9a6b8de36b8589499010218d5d013482c537dbbafc</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
